--- a/weekly_summary_layout_template.xlsx
+++ b/weekly_summary_layout_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrewfarrell/Desktop/muckspreading-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31219C9-6DE7-4A4E-82C7-D9C0B85BD4FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1191F1CC-EFA2-C14E-B35C-776A7726989E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="76">
   <si>
     <t>Weekly Jobs Summary</t>
   </si>
@@ -160,62 +160,101 @@
     <t>Compost</t>
   </si>
   <si>
-    <t>E. B Gowing &amp; Sons</t>
-  </si>
-  <si>
-    <t>General Muck</t>
-  </si>
-  <si>
-    <t>Friars Farm</t>
-  </si>
-  <si>
-    <t>G H Allen (Farms) Ltd</t>
-  </si>
-  <si>
-    <t>Genevieve Farms</t>
-  </si>
-  <si>
-    <t>Greens of Soham</t>
-  </si>
-  <si>
-    <t>H &amp; L Budgen</t>
-  </si>
-  <si>
-    <t>James Rodger &amp; Sons Ltd</t>
-  </si>
-  <si>
-    <t>JFQ Fenwick</t>
-  </si>
-  <si>
-    <t>Kidner Farming Ltd</t>
-  </si>
-  <si>
-    <t>Lamb Weston Meijer UK</t>
-  </si>
-  <si>
-    <t>M A &amp; H V Medlar</t>
-  </si>
-  <si>
-    <t>M P Howland</t>
-  </si>
-  <si>
-    <t>Mr G Gapp, Frith Farm</t>
-  </si>
-  <si>
-    <t>Mr M Adams</t>
-  </si>
-  <si>
     <t>Spreader Weight</t>
   </si>
   <si>
     <t>Ops Center Weight</t>
+  </si>
+  <si>
+    <t>Howe Hall</t>
+  </si>
+  <si>
+    <t>Mill Piece</t>
+  </si>
+  <si>
+    <t>Sandy Close</t>
+  </si>
+  <si>
+    <t>Laurel Farm</t>
+  </si>
+  <si>
+    <t>Station Field</t>
+  </si>
+  <si>
+    <t>Long Reach</t>
+  </si>
+  <si>
+    <t>Church Farm</t>
+  </si>
+  <si>
+    <t>East Side</t>
+  </si>
+  <si>
+    <t>Paddock End</t>
+  </si>
+  <si>
+    <t>Claxton</t>
+  </si>
+  <si>
+    <t>Rectory Field</t>
+  </si>
+  <si>
+    <t>Garden Meadow</t>
+  </si>
+  <si>
+    <t>Lower Hill</t>
+  </si>
+  <si>
+    <t>Oak Strip</t>
+  </si>
+  <si>
+    <t>Barn Field</t>
+  </si>
+  <si>
+    <t>Wash Meadow</t>
+  </si>
+  <si>
+    <t>South Acre</t>
+  </si>
+  <si>
+    <t>Outer Fen</t>
+  </si>
+  <si>
+    <t>School Piece</t>
+  </si>
+  <si>
+    <t>Hall Close</t>
+  </si>
+  <si>
+    <t>Boundary Farm</t>
+  </si>
+  <si>
+    <t>Hedge Field</t>
+  </si>
+  <si>
+    <t>Cross Leys</t>
+  </si>
+  <si>
+    <t>North Drove</t>
+  </si>
+  <si>
+    <t>Sentry</t>
+  </si>
+  <si>
+    <t>Pit Field</t>
+  </si>
+  <si>
+    <t>Chapel Meadow</t>
+  </si>
+  <si>
+    <t>River Piece</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -358,6 +397,14 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -540,7 +587,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -667,8 +714,19 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -718,12 +776,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1098,8 +1158,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F93"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="23.5" bestFit="1" customWidth="1"/>
@@ -1109,119 +1170,84 @@
     <col min="6" max="6" width="17.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Weekly Jobs Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>09 Mar 2026 to 15 Mar 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Jobs</t>
-        </is>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
       </c>
       <c r="B4">
         <v>48</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Spreader Tons</t>
-        </is>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>4</v>
       </c>
       <c r="B5">
         <v>1256.7</v>
       </c>
     </row>
-    <row r="6" ht="17" thickBot="1">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Ops Center Tons</t>
-        </is>
+    <row r="6" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="B6" s="1">
         <v>1046.8</v>
       </c>
     </row>
-    <row r="7" ht="17" thickTop="1"/>
-    <row r="8" ht="17" thickBot="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Customer / Farm</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Spreader Weight</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Ops Center Weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="17" thickTop="1"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>BB Farms Ltd</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Howe Hall</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>09 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Top Field</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Beet Spoil</t>
-        </is>
+    <row r="7" spans="1:6" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
       </c>
       <c r="E12">
         <v>16.2</v>
@@ -1230,21 +1256,15 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>09 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Top Field</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
       </c>
       <c r="E13">
         <v>17.7</v>
@@ -1253,121 +1273,90 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>10 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Mill Piece</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
       </c>
       <c r="E14">
         <v>20.6</v>
       </c>
       <c r="F14">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>10 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Mill Piece</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
       </c>
       <c r="E15">
-        <v>19.1</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="F15">
         <v>15.9</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>11 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Sandy Close</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Beet Spoil</t>
-        </is>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
       </c>
       <c r="E16">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="F16">
         <v>18.3</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Farm Totals</t>
-        </is>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4">
         <v>95.6</v>
       </c>
-      <c r="F17" s="2">
-        <v>79.60000000000001</v>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>C G Burridge &amp; Son</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Laurel Farm</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>12 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Home Meadow</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Cattle Muck</t>
-        </is>
+      <c r="F17" s="4">
+        <v>79.600000000000009</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
       </c>
       <c r="E21">
         <v>24.8</v>
@@ -1376,21 +1365,15 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>12 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Home Meadow</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
       </c>
       <c r="E22">
         <v>26.3</v>
@@ -1399,21 +1382,15 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>13 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Station Field</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Cattle Muck</t>
-        </is>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
       </c>
       <c r="E23">
         <v>29.2</v>
@@ -1422,21 +1399,15 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>13 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Station Field</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
       </c>
       <c r="E24">
         <v>27.7</v>
@@ -1445,21 +1416,15 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>14 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Long Reach</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" t="s">
+        <v>43</v>
       </c>
       <c r="E25">
         <v>30.6</v>
@@ -1468,52 +1433,39 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Farm Totals</t>
-        </is>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2">
+    <row r="26" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5">
         <v>138.6</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="5">
         <v>115.6</v>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Church Farm Partnership</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Church Farm</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>09 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>East Side</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
       </c>
       <c r="E30">
         <v>36.4</v>
@@ -1522,67 +1474,49 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>10 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Paddock End</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Chalk Lime</t>
-        </is>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" t="s">
+        <v>22</v>
       </c>
       <c r="E31">
-        <v>19.1</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="F31">
         <v>15.9</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>10 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Paddock End</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" t="s">
+        <v>26</v>
       </c>
       <c r="E32">
-        <v>17.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="F32">
         <v>14.7</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>15 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Back Field</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Chalk Lime</t>
-        </is>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" t="s">
+        <v>22</v>
       </c>
       <c r="E33">
         <v>33.5</v>
@@ -1591,121 +1525,90 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>15 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Back Field</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
       </c>
       <c r="E34">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="F34">
         <v>29.1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Farm Totals</t>
-        </is>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2">
+    <row r="35" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5">
         <v>141.6</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="5">
         <v>117.9</v>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Claxton Manor</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Claxton</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>11 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>North Piece</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" t="s">
+        <v>26</v>
       </c>
       <c r="E39">
         <v>20.5</v>
       </c>
       <c r="F39">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>11 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>North Piece</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" t="s">
+        <v>43</v>
       </c>
       <c r="E40">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="F40">
         <v>18.3</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>12 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Rectory Field</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" t="s">
+        <v>26</v>
       </c>
       <c r="E41">
         <v>23.4</v>
@@ -1714,21 +1617,15 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>13 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Garden Meadow</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" t="s">
+        <v>26</v>
       </c>
       <c r="E42">
         <v>27.8</v>
@@ -1737,21 +1634,15 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>13 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Garden Meadow</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" t="s">
+        <v>59</v>
+      </c>
+      <c r="D43" t="s">
+        <v>43</v>
       </c>
       <c r="E43">
         <v>26.3</v>
@@ -1760,52 +1651,39 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Farm Totals</t>
-        </is>
-      </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2">
-        <v>120.0</v>
-      </c>
-      <c r="F44" s="2">
+    <row r="44" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5">
+        <v>120</v>
+      </c>
+      <c r="F44" s="5">
         <v>99.9</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Crown Point Farms</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Bixley Farms</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>09 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Lower Hill</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Horse Muck</t>
-        </is>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48" t="s">
+        <v>31</v>
       </c>
       <c r="E48">
         <v>34.9</v>
@@ -1814,21 +1692,15 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>14 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>South Piece</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Horse Muck</t>
-        </is>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" t="s">
+        <v>31</v>
       </c>
       <c r="E49">
         <v>29.2</v>
@@ -1837,21 +1709,15 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>14 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>South Piece</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" t="s">
+        <v>43</v>
       </c>
       <c r="E50">
         <v>30.7</v>
@@ -1860,44 +1726,32 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>15 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Oak Strip</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" t="s">
+        <v>26</v>
       </c>
       <c r="E51">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="F51">
         <v>26.7</v>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>15 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Oak Strip</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" t="s">
+        <v>61</v>
+      </c>
+      <c r="D52" t="s">
+        <v>43</v>
       </c>
       <c r="E52">
         <v>33.5</v>
@@ -1906,45 +1760,34 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Farm Totals</t>
-        </is>
-      </c>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2">
-        <v>160.3</v>
-      </c>
-      <c r="F53" s="2">
+    <row r="53" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5">
+        <v>160.30000000000001</v>
+      </c>
+      <c r="F53" s="5">
         <v>133.5</v>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Crown Point Farms</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>10 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Long Close</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="s">
+        <v>33</v>
+      </c>
+      <c r="D56" t="s">
+        <v>26</v>
       </c>
       <c r="E56">
         <v>17.7</v>
@@ -1953,21 +1796,15 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>10 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Long Close</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Digestate</t>
-        </is>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57" t="s">
+        <v>34</v>
       </c>
       <c r="E57">
         <v>16.2</v>
@@ -1976,67 +1813,49 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>11 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Barn Field</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" t="s">
+        <v>62</v>
+      </c>
+      <c r="D58" t="s">
+        <v>43</v>
       </c>
       <c r="E58">
-        <v>19.1</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="F58">
         <v>15.9</v>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>12 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Wash Meadow</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Digestate</t>
-        </is>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" t="s">
+        <v>34</v>
       </c>
       <c r="E59">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="F59">
         <v>18.3</v>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>12 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Wash Meadow</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B60" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" t="s">
+        <v>63</v>
+      </c>
+      <c r="D60" t="s">
+        <v>43</v>
       </c>
       <c r="E60">
         <v>23.5</v>
@@ -2045,45 +1864,34 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Farm Totals</t>
-        </is>
-      </c>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2">
+    <row r="61" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5">
         <v>98.5</v>
       </c>
-      <c r="F61" s="2">
-        <v>82.0</v>
-      </c>
-    </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Octagon Farms</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>13 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Mill Field</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Duck Muck</t>
-        </is>
+      <c r="F61" s="5">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B64" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" t="s">
+        <v>37</v>
+      </c>
+      <c r="D64" t="s">
+        <v>38</v>
       </c>
       <c r="E64">
         <v>24.8</v>
@@ -2092,21 +1900,15 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>13 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Mill Field</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B65" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65" t="s">
+        <v>37</v>
+      </c>
+      <c r="D65" t="s">
+        <v>43</v>
       </c>
       <c r="E65">
         <v>26.3</v>
@@ -2115,21 +1917,15 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>14 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>South Acre</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B66" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66" t="s">
+        <v>64</v>
+      </c>
+      <c r="D66" t="s">
+        <v>26</v>
       </c>
       <c r="E66">
         <v>27.7</v>
@@ -2138,21 +1934,15 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>15 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Outer Fen</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
+        <v>36</v>
+      </c>
+      <c r="C67" t="s">
+        <v>65</v>
+      </c>
+      <c r="D67" t="s">
+        <v>26</v>
       </c>
       <c r="E67">
         <v>32.1</v>
@@ -2161,21 +1951,15 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>15 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Outer Fen</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Duck Muck</t>
-        </is>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B68" t="s">
+        <v>36</v>
+      </c>
+      <c r="C68" t="s">
+        <v>65</v>
+      </c>
+      <c r="D68" t="s">
+        <v>38</v>
       </c>
       <c r="E68">
         <v>30.6</v>
@@ -2184,68 +1968,51 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Farm Totals</t>
-        </is>
-      </c>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2">
+    <row r="69" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5">
         <v>141.5</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="5">
         <v>117.99999999999999</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>TAS Farms</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>09 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Bottom Field</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>40</v>
+      </c>
+      <c r="D72" t="s">
+        <v>43</v>
       </c>
       <c r="E72">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="F72">
         <v>29.1</v>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>09 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Bottom Field</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Pig Muck</t>
-        </is>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" t="s">
+        <v>40</v>
+      </c>
+      <c r="D73" t="s">
+        <v>41</v>
       </c>
       <c r="E73">
         <v>33.5</v>
@@ -2254,21 +2021,15 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>10 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>School Piece</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="s">
+        <v>66</v>
+      </c>
+      <c r="D74" t="s">
+        <v>26</v>
       </c>
       <c r="E74">
         <v>36.4</v>
@@ -2277,144 +2038,107 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>11 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Hall Close</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B75" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" t="s">
+        <v>67</v>
+      </c>
+      <c r="D75" t="s">
+        <v>26</v>
       </c>
       <c r="E75">
-        <v>19.1</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="F75">
         <v>15.9</v>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>11 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Hall Close</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Pig Muck</t>
-        </is>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B76" t="s">
+        <v>20</v>
+      </c>
+      <c r="C76" t="s">
+        <v>67</v>
+      </c>
+      <c r="D76" t="s">
+        <v>41</v>
       </c>
       <c r="E76">
-        <v>17.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="F76">
         <v>14.7</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Farm Totals</t>
-        </is>
-      </c>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2">
+    <row r="77" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5">
         <v>141.6</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="5">
         <v>117.9</v>
       </c>
     </row>
-    <row r="78"/>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>David Baker Farms Ltd</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Boundary Farm</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>12 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Hedge Field</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B81" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" t="s">
+        <v>69</v>
+      </c>
+      <c r="D81" t="s">
+        <v>26</v>
       </c>
       <c r="E81">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="F81">
         <v>18.3</v>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>12 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Hedge Field</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B82" t="s">
+        <v>24</v>
+      </c>
+      <c r="C82" t="s">
+        <v>69</v>
+      </c>
+      <c r="D82" t="s">
+        <v>43</v>
       </c>
       <c r="E82">
         <v>20.5</v>
       </c>
       <c r="F82">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>13 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Cross Leys</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B83" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" t="s">
+        <v>70</v>
+      </c>
+      <c r="D83" t="s">
+        <v>43</v>
       </c>
       <c r="E83">
         <v>23.4</v>
@@ -2423,21 +2147,15 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>14 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>North Drove</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B84" t="s">
+        <v>32</v>
+      </c>
+      <c r="C84" t="s">
+        <v>71</v>
+      </c>
+      <c r="D84" t="s">
+        <v>26</v>
       </c>
       <c r="E84">
         <v>26.3</v>
@@ -2446,75 +2164,56 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Farm Totals</t>
-        </is>
-      </c>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2">
+    <row r="85" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5">
         <v>92.2</v>
       </c>
-      <c r="F85" s="2">
-        <v>76.80000000000001</v>
-      </c>
-    </row>
-    <row r="86"/>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Ditchingham Farm No2 Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Sentry</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>09 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Pit Field</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Compost</t>
-        </is>
+      <c r="F85" s="5">
+        <v>76.800000000000011</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" t="s">
+        <v>73</v>
+      </c>
+      <c r="D89" t="s">
+        <v>45</v>
       </c>
       <c r="E89">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="F89">
         <v>26.7</v>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>10 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Chapel Meadow</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>LimeX 70</t>
-        </is>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="s">
+        <v>74</v>
+      </c>
+      <c r="D90" t="s">
+        <v>43</v>
       </c>
       <c r="E90">
         <v>34.9</v>
@@ -2523,21 +2222,15 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>15 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>River Piece</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Chicken Muck</t>
-        </is>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B91" t="s">
+        <v>36</v>
+      </c>
+      <c r="C91" t="s">
+        <v>75</v>
+      </c>
+      <c r="D91" t="s">
+        <v>26</v>
       </c>
       <c r="E91">
         <v>30.7</v>
@@ -2546,21 +2239,15 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>15 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>River Piece</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Compost</t>
-        </is>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B92" t="s">
+        <v>36</v>
+      </c>
+      <c r="C92" t="s">
+        <v>75</v>
+      </c>
+      <c r="D92" t="s">
+        <v>45</v>
       </c>
       <c r="E92">
         <v>29.2</v>
@@ -2569,23 +2256,20 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Farm Totals</t>
-        </is>
-      </c>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2">
+    <row r="93" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5">
         <v>126.80000000000001</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="5">
         <v>105.6</v>
       </c>
     </row>
-    <row r="94"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/weekly_summary_layout_template.xlsx
+++ b/weekly_summary_layout_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrewfarrell/Desktop/muckspreading-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1191F1CC-EFA2-C14E-B35C-776A7726989E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C601AD32-280E-BF42-BBE9-C199722ED156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -587,7 +587,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -717,15 +717,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -776,13 +767,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
@@ -1230,7 +1220,7 @@
     </row>
     <row r="9" spans="1:6" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1324,7 +1314,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
@@ -1339,7 +1329,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1434,21 +1424,21 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4">
         <v>138.6</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="4">
         <v>115.6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1543,21 +1533,21 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4">
         <v>141.6</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="4">
         <v>117.9</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1652,21 +1642,21 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5">
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4">
         <v>120</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="4">
         <v>99.9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1761,16 +1751,16 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5">
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4">
         <v>160.30000000000001</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="4">
         <v>133.5</v>
       </c>
     </row>
@@ -1865,16 +1855,16 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5">
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4">
         <v>98.5</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61" s="4">
         <v>82</v>
       </c>
     </row>
@@ -1969,16 +1959,16 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5">
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4">
         <v>141.5</v>
       </c>
-      <c r="F69" s="5">
+      <c r="F69" s="4">
         <v>117.99999999999999</v>
       </c>
     </row>
@@ -2073,21 +2063,21 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5">
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4">
         <v>141.6</v>
       </c>
-      <c r="F77" s="5">
+      <c r="F77" s="4">
         <v>117.9</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="5" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2165,21 +2155,21 @@
       </c>
     </row>
     <row r="85" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="5" t="s">
+      <c r="A85" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5">
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4">
         <v>92.2</v>
       </c>
-      <c r="F85" s="5">
+      <c r="F85" s="4">
         <v>76.800000000000011</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2257,16 +2247,16 @@
       </c>
     </row>
     <row r="93" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="5" t="s">
+      <c r="A93" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B93" s="5"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5">
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4">
         <v>126.80000000000001</v>
       </c>
-      <c r="F93" s="5">
+      <c r="F93" s="4">
         <v>105.6</v>
       </c>
     </row>
